--- a/作業/G3面接準備v2_kokura.xlsx
+++ b/作業/G3面接準備v2_kokura.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\000lib01.canon.net\aaa113012\G3\20210906_kokura\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnhan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F397B57D-F71A-4D92-AED5-9516D61DC5A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4AF29A-7969-44F5-A2D8-FF419353AA56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="210">
   <si>
     <t>質問</t>
     <rPh sb="0" eb="2">
@@ -5256,6 +5256,108 @@
   </si>
   <si>
     <t>x-2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>後輩はいない</t>
+    <rPh sb="0" eb="2">
+      <t>コウハイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>G2は、指示された業務を、自分の力で着実にこなすのが仕事です。
+対してG3は、自分の範囲を超え、周囲を巻き込みながら、リーダーシップを発揮して目標に突き進むのが役割です。
+(さらに突っ込まれたら)
+私は、事業部を巻き込んで、協力を引き出しています。
+以前、プライマと画質の関係を明らかにする際に、画像処理の専門の知見ではまとめきれない場面があった。その際に、インクの専門の人を巻き込んで、関係図を作成した。</t>
+    <rPh sb="126" eb="128">
+      <t>イゼン</t>
+    </rPh>
+    <rPh sb="134" eb="136">
+      <t>ガシツ</t>
+    </rPh>
+    <rPh sb="137" eb="139">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="140" eb="141">
+      <t>アキ</t>
+    </rPh>
+    <rPh sb="146" eb="147">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="149" eb="151">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="151" eb="153">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="154" eb="156">
+      <t>センモン</t>
+    </rPh>
+    <rPh sb="157" eb="159">
+      <t>チケン</t>
+    </rPh>
+    <rPh sb="168" eb="170">
+      <t>バメン</t>
+    </rPh>
+    <rPh sb="177" eb="178">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="184" eb="186">
+      <t>センモン</t>
+    </rPh>
+    <rPh sb="187" eb="188">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="189" eb="190">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="191" eb="192">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="195" eb="198">
+      <t>カンケイズ</t>
+    </rPh>
+    <rPh sb="199" eb="201">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>キヤノンの画質を世界一にしたい。
+今回開発した静止画のAI現像は、間違いなく世界一の性能。しかし、あくまで自部門の様々な高画質化アルゴリズムの一分野をAI化したに過ぎない。
+他にも高画質化技術は色々あり、〇〇すると多大な伸びしろがあって、全ての技術で他社を圧倒できる。
+G3になったら、様々な分野で高画質化のプロジェクトを立ち上げ、リソースを増やして主導していきたい。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>我々の部門においては、チームの開発の方向性をしっかり定めること、および後輩やチームメンバーの指導が重要になってくると考えています。
+製品化に向けて、課題分析や技術の見極め、どのようにチームで開発し実現していくかの見通しを立てる作業が必要です。
+あとは、後輩育成ですね。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">高画質化のスピード
+それに対処するために
+→メカニズム展開
+</t>
+    <rPh sb="0" eb="4">
+      <t>コウガシツカ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>タイショ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>テンカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同上</t>
+    <rPh sb="0" eb="2">
+      <t>ドウジョウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -5429,7 +5531,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5760,793 +5862,863 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.6328125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="50.36328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="119.08984375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="116.90625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="35.90625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="64.26953125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="111.6328125" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="2" max="3" width="50.36328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="119.08984375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="116.90625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="35.90625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="64.26953125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="111.6328125" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>118</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="13"/>
+      <c r="D1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="F1" s="14" t="s">
         <v>103</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>5</v>
       </c>
       <c r="G1" s="14" t="s">
         <v>5</v>
       </c>
+      <c r="H1" s="14" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" ht="104" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="104" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="65" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="65" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
     </row>
-    <row r="4" spans="1:7" ht="78" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="78" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="91" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="91" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>100</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="5"/>
+      <c r="D5" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
     </row>
-    <row r="6" spans="1:7" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="78.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="5"/>
+      <c r="D6" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="H6" s="8" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="39" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="E7" s="10" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="104" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="130" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>2</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="117" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="117" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>3</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="E9" s="9" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="143" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="143" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="E10" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="91" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="91" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="5"/>
+      <c r="D11" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="E11" s="10" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="26" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="26" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="10" t="s">
+      <c r="C12" s="5"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="10" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="143" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="143" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>4</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="E13" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
     </row>
-    <row r="14" spans="1:7" ht="26" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="26" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="9" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="65" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="65" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="5"/>
+      <c r="D15" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="E15" s="9" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="91" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="91" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="5"/>
+      <c r="D16" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="E16" s="9" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="52" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="52" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5"/>
+      <c r="D17" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="E17" s="9" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="78" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ht="78" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="9" t="s">
+      <c r="C18" s="5"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="9" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="78" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="78" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="5"/>
+      <c r="D19" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="E19" s="9" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="104" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" ht="104" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="5"/>
+      <c r="D20" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="26" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" ht="26" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>30</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5"/>
+      <c r="D21" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="E21" s="9" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="65" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" ht="65" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="5"/>
+      <c r="D22" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="E22" s="9" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="65" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="65" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5"/>
+      <c r="D23" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="E23" s="9" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="26" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ht="26" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="9" t="s">
+      <c r="C24" s="18"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="9" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="78" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" ht="78" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="9" t="s">
+      <c r="C25" s="5"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="9" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="39" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" ht="39" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="10" t="s">
+      <c r="C26" s="5"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="104" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" ht="104" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="5"/>
+      <c r="D27" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="E27" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="39" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" ht="39" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>43</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="5"/>
+      <c r="D28" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="E28" s="9" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="39" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" ht="39" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>44</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="5"/>
+      <c r="D29" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="D29" s="9"/>
-      <c r="F29" s="3" t="s">
+      <c r="E29" s="9"/>
+      <c r="G29" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="52" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" ht="52" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>45</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="9" t="s">
+      <c r="C30" s="5"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="G30" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="39" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" ht="39" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>47</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="5"/>
+      <c r="D31" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="E31" s="9" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="39" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" ht="39" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>49</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="5"/>
+      <c r="D32" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="D32" s="7"/>
-      <c r="F32" s="3" t="s">
+      <c r="E32" s="7"/>
+      <c r="G32" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
     </row>
-    <row r="33" spans="1:6" ht="39" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" ht="39" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>50</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="5"/>
+      <c r="D33" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="E33" s="9" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="26" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" ht="26" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>52</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="9" t="s">
+      <c r="C34" s="5"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="9" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="65" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" ht="65" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="5"/>
+      <c r="D35" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="E35" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="G35" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="52" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" ht="52" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>56</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="5"/>
+      <c r="D36" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="E36" s="9" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="65" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" ht="65" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>58</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="5"/>
+      <c r="D37" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="E37" s="9" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="65" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" ht="65" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>60</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="5"/>
+      <c r="D38" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="E38" s="10" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="91" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" ht="91" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>61</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="11" t="s">
+      <c r="C39" s="5"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="G39" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>63</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="7"/>
+      <c r="C40" s="5"/>
       <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
     </row>
-    <row r="41" spans="1:6" ht="26" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" ht="26" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>65</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="7"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
     </row>
-    <row r="42" spans="1:6" ht="26" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" ht="26" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>67</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C42" s="7"/>
+      <c r="C42" s="5"/>
       <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
     </row>
-    <row r="43" spans="1:6" ht="130" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" ht="130" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>69</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="5"/>
+      <c r="D43" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D43" s="7"/>
-      <c r="F43" s="3" t="s">
+      <c r="E43" s="7"/>
+      <c r="G43" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="65" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" ht="65" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>70</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="5"/>
+      <c r="D44" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="D44" s="7"/>
-      <c r="F44" s="3" t="s">
+      <c r="E44" s="7"/>
+      <c r="G44" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="26" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" ht="26" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>71</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="5"/>
+      <c r="D45" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
     </row>
-    <row r="46" spans="1:6" ht="26" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" ht="26" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>73</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C46" s="17"/>
-      <c r="D46" s="7"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="7"/>
     </row>
-    <row r="47" spans="1:6" ht="26" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" ht="26" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>75</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C47" s="17"/>
-      <c r="D47" s="7"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="7"/>
     </row>
-    <row r="48" spans="1:6" ht="26" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" ht="26" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>77</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C48" s="7"/>
+      <c r="C48" s="5"/>
       <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
     </row>
-    <row r="49" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" ht="39" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>79</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="5"/>
+      <c r="D49" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
     </row>
-    <row r="50" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" ht="39" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>81</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="5"/>
+      <c r="D50" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
     </row>
-    <row r="51" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" ht="39" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>98</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="5"/>
+      <c r="D51" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
     </row>
-    <row r="52" spans="1:4" ht="91" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" ht="91" x14ac:dyDescent="0.2">
       <c r="A52" s="4"/>
       <c r="B52" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="5"/>
+      <c r="D52" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
       <c r="B53" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="C53" s="7"/>
+      <c r="C53" s="5"/>
       <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
     </row>
-    <row r="54" spans="1:4" ht="26" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" ht="26" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
       <c r="B54" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="5"/>
+      <c r="D54" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="4"/>
       <c r="B55" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="5"/>
+      <c r="D55" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
     </row>
-    <row r="56" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" ht="39" x14ac:dyDescent="0.2">
       <c r="A56" s="4"/>
       <c r="B56" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="5"/>
+      <c r="D56" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
     </row>
-    <row r="57" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" ht="39" x14ac:dyDescent="0.2">
       <c r="A57" s="4"/>
       <c r="B57" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="5"/>
+      <c r="D57" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" s="4"/>
       <c r="B58" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C58" s="7"/>
+      <c r="C58" s="5"/>
       <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
     </row>
-    <row r="59" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" ht="78" x14ac:dyDescent="0.2">
       <c r="A59" s="4"/>
       <c r="B59" s="5" t="s">
         <v>113</v>
@@ -6554,32 +6726,37 @@
       <c r="C59" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D59" s="7"/>
+      <c r="D59" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E59" s="7"/>
     </row>
-    <row r="60" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" ht="39" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>202</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="5"/>
+      <c r="D60" s="7" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="61" spans="1:4" ht="39" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" ht="39" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>203</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="5"/>
+      <c r="D61" s="7" t="s">
         <v>200</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="14" fitToHeight="0" orientation="portrait" r:id="rId1"/>
